--- a/RPO_SaaS_Project_Breakdown2.xlsx
+++ b/RPO_SaaS_Project_Breakdown2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\RandR\Jobstock_Django_v1.0.0\Jobstock_Django\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA8CAA1F-3AD5-4697-86A9-B9D3D3BAED9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4FF5D7F-9541-44FF-B550-76D1676A76FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Overview" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1645" uniqueCount="818">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1607" uniqueCount="797">
   <si>
     <t>RPO SaaS Tool - Rudra Recruiter AI</t>
   </si>
@@ -1200,51 +1200,30 @@
     <t>₹ 20,70,000</t>
   </si>
   <si>
-    <t>₹ 57,00,000</t>
-  </si>
-  <si>
     <t>80,000</t>
   </si>
   <si>
     <t>4,80,000</t>
   </si>
   <si>
-    <t>13,50,000</t>
-  </si>
-  <si>
-    <t>70,000</t>
-  </si>
-  <si>
     <t>4,20,000</t>
   </si>
   <si>
-    <t>11,70,000</t>
-  </si>
-  <si>
     <t>ML/AI Engineer</t>
   </si>
   <si>
     <t>1,00,000</t>
   </si>
   <si>
-    <t>2,00,000</t>
-  </si>
-  <si>
     <t>4,00,000</t>
   </si>
   <si>
-    <t>12,00,000</t>
-  </si>
-  <si>
     <t>UI/UX Designer</t>
   </si>
   <si>
     <t>50,000</t>
   </si>
   <si>
-    <t>3,00,000</t>
-  </si>
-  <si>
     <t>QA Engineer</t>
   </si>
   <si>
@@ -1263,15 +1242,9 @@
     <t>3,60,000</t>
   </si>
   <si>
-    <t>7,20,000</t>
-  </si>
-  <si>
     <t>Solution Architect (Consultant)</t>
   </si>
   <si>
-    <t>3,50,000</t>
-  </si>
-  <si>
     <t>Technical Writer</t>
   </si>
   <si>
@@ -1296,9 +1269,6 @@
     <t>Min Total (INR)</t>
   </si>
   <si>
-    <t>Max Total (INR)</t>
-  </si>
-  <si>
     <t>Human Resources</t>
   </si>
   <si>
@@ -1344,9 +1314,6 @@
     <t>70,000/month</t>
   </si>
   <si>
-    <t>6,30,000</t>
-  </si>
-  <si>
     <t>Alternative to senior</t>
   </si>
   <si>
@@ -1419,9 +1386,6 @@
     <t>5,000</t>
   </si>
   <si>
-    <t>10,000</t>
-  </si>
-  <si>
     <t>Custom domain and security</t>
   </si>
   <si>
@@ -1464,9 +1428,6 @@
     <t>₹ 5,81,000</t>
   </si>
   <si>
-    <t>₹ 10,90,000</t>
-  </si>
-  <si>
     <t>Software &amp; Tools</t>
   </si>
   <si>
@@ -1479,9 +1440,6 @@
     <t>14,400</t>
   </si>
   <si>
-    <t>21,600</t>
-  </si>
-  <si>
     <t>Design collaboration</t>
   </si>
   <si>
@@ -1497,9 +1455,6 @@
     <t>25,200</t>
   </si>
   <si>
-    <t>42,000</t>
-  </si>
-  <si>
     <t>Development tools</t>
   </si>
   <si>
@@ -1533,9 +1488,6 @@
     <t>₹ 2,43,600</t>
   </si>
   <si>
-    <t>₹ 3,79,600</t>
-  </si>
-  <si>
     <t>API &amp; Integrations</t>
   </si>
   <si>
@@ -1581,9 +1533,6 @@
     <t>₹ 9,50,000</t>
   </si>
   <si>
-    <t>₹ 14,20,000</t>
-  </si>
-  <si>
     <t>Phase II features</t>
   </si>
   <si>
@@ -1638,9 +1587,6 @@
     <t>2,07,000</t>
   </si>
   <si>
-    <t>5,70,000</t>
-  </si>
-  <si>
     <t>Unexpected expenses</t>
   </si>
   <si>
@@ -1650,18 +1596,12 @@
     <t>₹ 5,07,000</t>
   </si>
   <si>
-    <t>₹ 12,70,000</t>
-  </si>
-  <si>
     <t>TOTAL MVP COST</t>
   </si>
   <si>
     <t>₹ 34,01,600</t>
   </si>
   <si>
-    <t>₹ 81,89,600</t>
-  </si>
-  <si>
     <t>Minimum viable product</t>
   </si>
   <si>
@@ -1669,9 +1609,6 @@
   </si>
   <si>
     <t>₹ 43,51,600</t>
-  </si>
-  <si>
-    <t>₹ 96,09,600</t>
   </si>
   <si>
     <t>Including Phase II features</t>
@@ -3228,19 +3165,19 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>702</v>
+        <v>681</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>703</v>
+        <v>682</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>704</v>
+        <v>683</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>705</v>
+        <v>684</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>706</v>
+        <v>685</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>38</v>
@@ -3251,19 +3188,19 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>707</v>
+        <v>686</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>708</v>
+        <v>687</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>709</v>
+        <v>688</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>710</v>
+        <v>689</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>711</v>
+        <v>690</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>82</v>
@@ -3274,19 +3211,19 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>712</v>
+        <v>691</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>708</v>
+        <v>687</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>713</v>
+        <v>692</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>714</v>
+        <v>693</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>715</v>
+        <v>694</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>82</v>
@@ -3297,19 +3234,19 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>716</v>
+        <v>695</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>708</v>
+        <v>687</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>717</v>
+        <v>696</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>718</v>
+        <v>697</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>719</v>
+        <v>698</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>82</v>
@@ -3320,19 +3257,19 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>720</v>
+        <v>699</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>708</v>
+        <v>687</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>721</v>
+        <v>700</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>722</v>
+        <v>701</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>723</v>
+        <v>702</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>67</v>
@@ -3343,19 +3280,19 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>724</v>
+        <v>703</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>725</v>
+        <v>704</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>726</v>
+        <v>705</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>727</v>
+        <v>706</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>728</v>
+        <v>707</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>82</v>
@@ -3366,19 +3303,19 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>729</v>
+        <v>708</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>725</v>
+        <v>704</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>730</v>
+        <v>709</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>517</v>
+        <v>500</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>731</v>
+        <v>710</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>82</v>
@@ -3389,19 +3326,19 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>729</v>
+        <v>708</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>732</v>
+        <v>711</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>733</v>
+        <v>712</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>734</v>
+        <v>713</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>719</v>
+        <v>698</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>82</v>
@@ -3412,19 +3349,19 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>729</v>
+        <v>708</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>735</v>
+        <v>714</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>736</v>
+        <v>715</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>517</v>
+        <v>500</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>719</v>
+        <v>698</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>82</v>
@@ -3435,19 +3372,19 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>737</v>
+        <v>716</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>708</v>
+        <v>687</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>738</v>
+        <v>717</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>739</v>
+        <v>718</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>740</v>
+        <v>719</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>67</v>
@@ -3458,19 +3395,19 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>741</v>
+        <v>720</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>708</v>
+        <v>687</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>742</v>
+        <v>721</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>743</v>
+        <v>722</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>744</v>
+        <v>723</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>82</v>
@@ -3481,19 +3418,19 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>741</v>
+        <v>720</v>
       </c>
       <c r="B12" s="5" t="s">
+        <v>704</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>724</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>706</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>725</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>745</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>727</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>746</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>82</v>
@@ -3504,19 +3441,19 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>747</v>
+        <v>726</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>725</v>
+        <v>704</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>748</v>
+        <v>727</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>517</v>
+        <v>500</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>749</v>
+        <v>728</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>82</v>
@@ -3527,19 +3464,19 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>747</v>
+        <v>726</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>732</v>
+        <v>711</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>750</v>
+        <v>729</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>734</v>
+        <v>713</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>719</v>
+        <v>698</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>82</v>
@@ -3550,19 +3487,19 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>747</v>
+        <v>726</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>735</v>
+        <v>714</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>751</v>
+        <v>730</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>517</v>
+        <v>500</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>719</v>
+        <v>698</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>82</v>
@@ -3573,19 +3510,19 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>752</v>
+        <v>731</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>725</v>
+        <v>704</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>753</v>
+        <v>732</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>517</v>
+        <v>500</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>754</v>
+        <v>733</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>67</v>
@@ -3596,19 +3533,19 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>755</v>
+        <v>734</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>708</v>
+        <v>687</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>756</v>
+        <v>735</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>757</v>
+        <v>736</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>758</v>
+        <v>737</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>71</v>
@@ -3619,19 +3556,19 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>759</v>
+        <v>738</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>708</v>
+        <v>687</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>760</v>
+        <v>739</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>761</v>
+        <v>740</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>719</v>
+        <v>698</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>82</v>
@@ -3642,19 +3579,19 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>762</v>
+        <v>741</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>725</v>
+        <v>704</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>763</v>
+        <v>742</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>517</v>
+        <v>500</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>764</v>
+        <v>743</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>82</v>
@@ -3665,19 +3602,19 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>765</v>
+        <v>744</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>725</v>
+        <v>704</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>766</v>
+        <v>745</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>767</v>
+        <v>746</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>768</v>
+        <v>747</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>82</v>
@@ -3688,19 +3625,19 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>708</v>
+        <v>687</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>770</v>
+        <v>749</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>771</v>
+        <v>750</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>772</v>
+        <v>751</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>82</v>
@@ -3711,19 +3648,19 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>773</v>
+        <v>752</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>708</v>
+        <v>687</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>774</v>
+        <v>753</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>775</v>
+        <v>754</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>719</v>
+        <v>698</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>82</v>
@@ -3734,19 +3671,19 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>776</v>
+        <v>755</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>725</v>
+        <v>704</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>777</v>
+        <v>756</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>778</v>
+        <v>757</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>779</v>
+        <v>758</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>82</v>
@@ -3757,19 +3694,19 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>780</v>
+        <v>759</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>708</v>
+        <v>687</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>781</v>
+        <v>760</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>782</v>
+        <v>761</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>783</v>
+        <v>762</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>82</v>
@@ -3798,19 +3735,19 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>784</v>
+        <v>763</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>785</v>
+        <v>764</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>786</v>
+        <v>765</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>787</v>
+        <v>766</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>788</v>
+        <v>767</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>371</v>
@@ -3818,102 +3755,102 @@
     </row>
     <row r="2" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>789</v>
+        <v>768</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>790</v>
+        <v>769</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>791</v>
+        <v>770</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>792</v>
+        <v>771</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>793</v>
+        <v>772</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>794</v>
+        <v>773</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>795</v>
+        <v>774</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>796</v>
+        <v>775</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>797</v>
+        <v>776</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>798</v>
+        <v>777</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>799</v>
+        <v>778</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>800</v>
+        <v>779</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>801</v>
+        <v>780</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>796</v>
+        <v>775</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>802</v>
+        <v>781</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>803</v>
+        <v>782</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>804</v>
+        <v>783</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>805</v>
+        <v>784</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>806</v>
+        <v>785</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>807</v>
+        <v>786</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>808</v>
+        <v>787</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>809</v>
+        <v>788</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>810</v>
+        <v>789</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>811</v>
+        <v>790</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>812</v>
+        <v>791</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>813</v>
+        <v>792</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>814</v>
+        <v>793</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>815</v>
+        <v>794</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>816</v>
+        <v>795</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>817</v>
+        <v>796</v>
       </c>
     </row>
   </sheetData>
@@ -6934,847 +6871,732 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="35" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="40" customWidth="1"/>
+    <col min="4" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>400</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>401</v>
       </c>
-      <c r="C1" s="4" t="s">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>402</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="C3" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E3" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>404</v>
       </c>
-      <c r="F1" s="4" t="s">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="G1" s="4" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="C4" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>408</v>
       </c>
-      <c r="D2" s="5" t="s">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>409</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="C5" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>410</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="E5" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>406</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="C6" s="5" t="s">
         <v>412</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>408</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="D6" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>413</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="G3" s="5" t="s">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>406</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="D7" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>415</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>408</v>
-      </c>
-      <c r="D4" s="5" t="s">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>416</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="C8" s="5" t="s">
         <v>417</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>379</v>
-      </c>
-      <c r="G4" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>418</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>406</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="E8" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>408</v>
-      </c>
-      <c r="D5" s="5" t="s">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>420</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="F5" s="5" t="s">
+      <c r="E9" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>421</v>
       </c>
-      <c r="G5" s="5" t="s">
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>406</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>380</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="C10" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>384</v>
-      </c>
-      <c r="G6" s="5" t="s">
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>406</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>385</v>
-      </c>
-      <c r="C7" s="5" t="s">
+      <c r="E11" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>420</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>387</v>
-      </c>
-      <c r="G7" s="5" t="s">
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>406</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>427</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>387</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>406</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>388</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>425</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>389</v>
-      </c>
-      <c r="F9" s="5" t="s">
+      <c r="E12" s="5" t="s">
         <v>390</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>406</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>433</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>423</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>393</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>406</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>395</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>398</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>435</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>396</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>406</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>397</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>398</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>399</v>
-      </c>
       <c r="F12" s="5" t="s">
-        <v>377</v>
-      </c>
-      <c r="G12" s="5" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="11" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="E13" s="12" t="s">
         <v>372</v>
       </c>
-      <c r="F13" s="12" t="s">
-        <v>373</v>
-      </c>
-      <c r="G13" s="5"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F13" s="5"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>142</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>142</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>142</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>142</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="C17" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>440</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>452</v>
-      </c>
       <c r="E17" s="5" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>453</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>142</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>391</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
       <c r="D19" s="11" t="s">
+        <v>447</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>448</v>
+      </c>
+      <c r="F19" s="5"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>459</v>
       </c>
-      <c r="E19" s="12" t="s">
+      <c r="C22" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="F22" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="F19" s="12" t="s">
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>461</v>
       </c>
-      <c r="G19" s="5"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
+      <c r="C23" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="F23" s="5" t="s">
         <v>462</v>
       </c>
-      <c r="B20" s="5" t="s">
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>463</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>440</v>
-      </c>
-      <c r="D20" s="5" t="s">
+      <c r="C24" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D24" s="5" t="s">
         <v>464</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E24" s="5" t="s">
         <v>465</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F24" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="G20" s="5" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
-        <v>462</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>468</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>469</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>470</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>471</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>472</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
-        <v>462</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>474</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>440</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>452</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>453</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
-        <v>462</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>476</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>440</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>391</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
-        <v>462</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>478</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>440</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>479</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>480</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>457</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
       <c r="D25" s="11" t="s">
-        <v>482</v>
+        <v>467</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>483</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>484</v>
-      </c>
-      <c r="G25" s="5"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+        <v>468</v>
+      </c>
+      <c r="F25" s="5"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>485</v>
+        <v>469</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>486</v>
+        <v>470</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>487</v>
+        <v>471</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>485</v>
+        <v>469</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>489</v>
+        <v>473</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>490</v>
+        <v>474</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>393</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>485</v>
+        <v>469</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>492</v>
+        <v>476</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>493</v>
+        <v>477</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>390</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>485</v>
+        <v>469</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>495</v>
+        <v>479</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
       <c r="D30" s="11" t="s">
+        <v>482</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>483</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>486</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>490</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>491</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>494</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="B35" s="5" t="s">
         <v>498</v>
       </c>
-      <c r="E30" s="12" t="s">
+      <c r="C35" s="5" t="s">
         <v>499</v>
       </c>
-      <c r="F30" s="12" t="s">
+      <c r="D35" s="5" t="s">
         <v>500</v>
       </c>
-      <c r="G30" s="5" t="s">
+      <c r="E35" s="5" t="s">
         <v>501</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
+      <c r="F35" s="5" t="s">
         <v>502</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>503</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>504</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>505</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
-        <v>502</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>507</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>508</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
-        <v>502</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>510</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>511</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
-        <v>502</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>513</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>496</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="5" t="s">
-        <v>502</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>515</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>516</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>517</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>518</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>519</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
       <c r="D36" s="11" t="s">
-        <v>521</v>
+        <v>503</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>522</v>
-      </c>
-      <c r="F36" s="12" t="s">
-        <v>523</v>
-      </c>
-      <c r="G36" s="5"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+        <v>504</v>
+      </c>
+      <c r="F36" s="5"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-    </row>
-    <row r="38" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
-        <v>524</v>
+        <v>505</v>
       </c>
       <c r="B38" s="13"/>
       <c r="C38" s="13"/>
       <c r="D38" s="13"/>
       <c r="E38" s="12" t="s">
-        <v>525</v>
-      </c>
-      <c r="F38" s="12" t="s">
-        <v>526</v>
-      </c>
-      <c r="G38" s="13" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+        <v>506</v>
+      </c>
+      <c r="F38" s="13" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
-        <v>528</v>
+        <v>508</v>
       </c>
       <c r="B39" s="13"/>
       <c r="C39" s="13"/>
       <c r="D39" s="13"/>
       <c r="E39" s="12" t="s">
-        <v>529</v>
-      </c>
-      <c r="F39" s="12" t="s">
-        <v>530</v>
-      </c>
-      <c r="G39" s="13" t="s">
-        <v>531</v>
+        <v>509</v>
+      </c>
+      <c r="F39" s="13" t="s">
+        <v>510</v>
       </c>
     </row>
   </sheetData>
@@ -7792,19 +7614,19 @@
   <sheetData>
     <row r="1" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>532</v>
+        <v>511</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>533</v>
+        <v>512</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>534</v>
+        <v>513</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>535</v>
+        <v>514</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>40</v>
@@ -7815,14 +7637,14 @@
         <v>196</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>536</v>
+        <v>515</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>537</v>
+        <v>516</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="5" t="s">
-        <v>538</v>
+        <v>517</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>48</v>
@@ -7833,36 +7655,36 @@
         <v>196</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>539</v>
+        <v>518</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>540</v>
+        <v>519</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>541</v>
+        <v>520</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>542</v>
+        <v>521</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>196</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>543</v>
+        <v>522</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>544</v>
+        <v>523</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>545</v>
+        <v>524</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>546</v>
+        <v>525</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>68</v>
@@ -7870,19 +7692,19 @@
     </row>
     <row r="5" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>547</v>
+        <v>526</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>548</v>
+        <v>527</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>549</v>
+        <v>528</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>550</v>
+        <v>529</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>551</v>
+        <v>530</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>68</v>
@@ -7890,99 +7712,99 @@
     </row>
     <row r="6" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>547</v>
+        <v>526</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>552</v>
+        <v>531</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>553</v>
+        <v>532</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>554</v>
+        <v>533</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>555</v>
+        <v>534</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>547</v>
+        <v>526</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>557</v>
+        <v>536</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>558</v>
+        <v>537</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>554</v>
+        <v>533</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>559</v>
+        <v>538</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>547</v>
+        <v>526</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>560</v>
+        <v>539</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>561</v>
+        <v>540</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>562</v>
+        <v>541</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>563</v>
+        <v>542</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>564</v>
+        <v>543</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>565</v>
+        <v>544</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>566</v>
+        <v>545</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>554</v>
+        <v>533</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>567</v>
+        <v>546</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>564</v>
+        <v>543</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>568</v>
+        <v>547</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>569</v>
+        <v>548</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>570</v>
+        <v>549</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>571</v>
+        <v>550</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>48</v>
@@ -7990,39 +7812,39 @@
     </row>
     <row r="11" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>564</v>
+        <v>543</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>572</v>
+        <v>551</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>573</v>
+        <v>552</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>574</v>
+        <v>553</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>575</v>
+        <v>554</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>564</v>
+        <v>543</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>576</v>
+        <v>555</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>577</v>
+        <v>556</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>578</v>
+        <v>557</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>579</v>
+        <v>558</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>68</v>
@@ -8030,19 +7852,19 @@
     </row>
     <row r="13" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>580</v>
+        <v>559</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>186</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>581</v>
+        <v>560</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>582</v>
+        <v>561</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>583</v>
+        <v>562</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>68</v>
@@ -8050,19 +7872,19 @@
     </row>
     <row r="14" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>580</v>
+        <v>559</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>584</v>
+        <v>563</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>585</v>
+        <v>564</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>586</v>
+        <v>565</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>587</v>
+        <v>566</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>68</v>
@@ -8070,59 +7892,59 @@
     </row>
     <row r="15" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>580</v>
+        <v>559</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>588</v>
+        <v>567</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>589</v>
+        <v>568</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>590</v>
+        <v>569</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>591</v>
+        <v>570</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>580</v>
+        <v>559</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>592</v>
+        <v>571</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>593</v>
+        <v>572</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>594</v>
+        <v>573</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>595</v>
+        <v>574</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="105" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>596</v>
+        <v>575</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>597</v>
+        <v>576</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>598</v>
+        <v>577</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>599</v>
+        <v>578</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>600</v>
+        <v>579</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>68</v>
@@ -8130,62 +7952,62 @@
     </row>
     <row r="18" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>596</v>
+        <v>575</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>601</v>
+        <v>580</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>602</v>
+        <v>581</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>603</v>
+        <v>582</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>604</v>
+        <v>583</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>605</v>
+        <v>584</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>606</v>
+        <v>585</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>607</v>
+        <v>586</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>596</v>
+        <v>575</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>608</v>
+        <v>587</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>609</v>
+        <v>588</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>605</v>
+        <v>584</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>610</v>
+        <v>589</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>607</v>
+        <v>586</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>596</v>
+        <v>575</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>611</v>
+        <v>590</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>609</v>
+        <v>588</v>
       </c>
     </row>
   </sheetData>
@@ -8208,19 +8030,19 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>532</v>
+        <v>511</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>533</v>
+        <v>512</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>534</v>
+        <v>513</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>535</v>
+        <v>514</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>40</v>
@@ -8231,14 +8053,14 @@
         <v>196</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>536</v>
+        <v>515</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>537</v>
+        <v>516</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="5" t="s">
-        <v>538</v>
+        <v>517</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>48</v>
@@ -8249,16 +8071,16 @@
         <v>196</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>539</v>
+        <v>518</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>540</v>
+        <v>519</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>541</v>
+        <v>520</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>542</v>
+        <v>521</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>68</v>
@@ -8269,16 +8091,16 @@
         <v>196</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>543</v>
+        <v>522</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>544</v>
+        <v>523</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>545</v>
+        <v>524</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>546</v>
+        <v>525</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>68</v>
@@ -8286,19 +8108,19 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>547</v>
+        <v>526</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>548</v>
+        <v>527</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>549</v>
+        <v>528</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>550</v>
+        <v>529</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>551</v>
+        <v>530</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>68</v>
@@ -8306,39 +8128,39 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>547</v>
+        <v>526</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>552</v>
+        <v>531</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>553</v>
+        <v>532</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>554</v>
+        <v>533</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>555</v>
+        <v>534</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>556</v>
+        <v>535</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>547</v>
+        <v>526</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>557</v>
+        <v>536</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>558</v>
+        <v>537</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>554</v>
+        <v>533</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>559</v>
+        <v>538</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>52</v>
@@ -8346,19 +8168,19 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>547</v>
+        <v>526</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>560</v>
+        <v>539</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>561</v>
+        <v>540</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>562</v>
+        <v>541</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>563</v>
+        <v>542</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>48</v>
@@ -8366,19 +8188,19 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>564</v>
+        <v>543</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>565</v>
+        <v>544</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>566</v>
+        <v>545</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>554</v>
+        <v>533</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>567</v>
+        <v>546</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>68</v>
@@ -8386,19 +8208,19 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>564</v>
+        <v>543</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>568</v>
+        <v>547</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>569</v>
+        <v>548</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>570</v>
+        <v>549</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>571</v>
+        <v>550</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>48</v>
@@ -8406,19 +8228,19 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>564</v>
+        <v>543</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>572</v>
+        <v>551</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>573</v>
+        <v>552</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>574</v>
+        <v>553</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>575</v>
+        <v>554</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>68</v>
@@ -8426,19 +8248,19 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>564</v>
+        <v>543</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>576</v>
+        <v>555</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>577</v>
+        <v>556</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>578</v>
+        <v>557</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>579</v>
+        <v>558</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>68</v>
@@ -8446,19 +8268,19 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>580</v>
+        <v>559</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>186</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>581</v>
+        <v>560</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>582</v>
+        <v>561</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>583</v>
+        <v>562</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>68</v>
@@ -8466,19 +8288,19 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>580</v>
+        <v>559</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>584</v>
+        <v>563</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>585</v>
+        <v>564</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>586</v>
+        <v>565</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>587</v>
+        <v>566</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>68</v>
@@ -8486,19 +8308,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>580</v>
+        <v>559</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>588</v>
+        <v>567</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>589</v>
+        <v>568</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>590</v>
+        <v>569</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>591</v>
+        <v>570</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>68</v>
@@ -8506,19 +8328,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>580</v>
+        <v>559</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>592</v>
+        <v>571</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>593</v>
+        <v>572</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>594</v>
+        <v>573</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>595</v>
+        <v>574</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>68</v>
@@ -8526,19 +8348,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>596</v>
+        <v>575</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>597</v>
+        <v>576</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>598</v>
+        <v>577</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>599</v>
+        <v>578</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>600</v>
+        <v>579</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>68</v>
@@ -8546,19 +8368,19 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>596</v>
+        <v>575</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>601</v>
+        <v>580</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>602</v>
+        <v>581</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>603</v>
+        <v>582</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>604</v>
+        <v>583</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>68</v>
@@ -8566,42 +8388,42 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>605</v>
+        <v>584</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>606</v>
+        <v>585</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>607</v>
+        <v>586</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>596</v>
+        <v>575</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>608</v>
+        <v>587</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>609</v>
+        <v>588</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>605</v>
+        <v>584</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>610</v>
+        <v>589</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>607</v>
+        <v>586</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>596</v>
+        <v>575</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>611</v>
+        <v>590</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>609</v>
+        <v>588</v>
       </c>
     </row>
   </sheetData>
@@ -8625,13 +8447,13 @@
         <v>3</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>612</v>
+        <v>591</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>613</v>
+        <v>592</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>614</v>
+        <v>593</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>371</v>
@@ -8639,155 +8461,155 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>615</v>
+        <v>594</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>616</v>
+        <v>595</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>617</v>
+        <v>596</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>618</v>
+        <v>597</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>619</v>
+        <v>598</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>620</v>
+        <v>599</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>621</v>
+        <v>600</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>622</v>
+        <v>601</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>623</v>
+        <v>602</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>624</v>
+        <v>603</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>625</v>
+        <v>604</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>626</v>
+        <v>605</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>627</v>
+        <v>606</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>628</v>
+        <v>607</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>629</v>
+        <v>608</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>625</v>
+        <v>604</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>630</v>
+        <v>609</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>631</v>
+        <v>610</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>632</v>
+        <v>611</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>633</v>
+        <v>612</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>634</v>
+        <v>613</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>635</v>
+        <v>614</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>636</v>
+        <v>615</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>637</v>
+        <v>616</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>638</v>
+        <v>617</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>639</v>
+        <v>618</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>640</v>
+        <v>619</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>641</v>
+        <v>620</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>642</v>
+        <v>621</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>643</v>
+        <v>622</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>644</v>
+        <v>623</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>645</v>
+        <v>624</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>646</v>
+        <v>625</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>647</v>
+        <v>626</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>648</v>
+        <v>627</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>649</v>
+        <v>628</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>650</v>
+        <v>629</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>651</v>
+        <v>630</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>652</v>
+        <v>631</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>653</v>
+        <v>632</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>654</v>
+        <v>633</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>655</v>
+        <v>634</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>656</v>
+        <v>635</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>657</v>
+        <v>636</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>658</v>
+        <v>637</v>
       </c>
     </row>
   </sheetData>
@@ -8810,30 +8632,30 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>659</v>
+        <v>638</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>660</v>
+        <v>639</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>661</v>
+        <v>640</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>662</v>
+        <v>641</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>663</v>
+        <v>642</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>664</v>
+        <v>643</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>665</v>
+        <v>644</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>666</v>
+        <v>645</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>49</v>
@@ -8842,18 +8664,18 @@
         <v>60</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>667</v>
+        <v>646</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>668</v>
+        <v>647</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>669</v>
+        <v>648</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>670</v>
+        <v>649</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>60</v>
@@ -8862,18 +8684,18 @@
         <v>49</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>671</v>
+        <v>650</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>672</v>
+        <v>651</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>673</v>
+        <v>652</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>674</v>
+        <v>653</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>49</v>
@@ -8882,18 +8704,18 @@
         <v>60</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>675</v>
+        <v>654</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>676</v>
+        <v>655</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>677</v>
+        <v>656</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>678</v>
+        <v>657</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>60</v>
@@ -8902,18 +8724,18 @@
         <v>60</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>679</v>
+        <v>658</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>680</v>
+        <v>659</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>681</v>
+        <v>660</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>682</v>
+        <v>661</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>49</v>
@@ -8922,18 +8744,18 @@
         <v>49</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>683</v>
+        <v>662</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>672</v>
+        <v>651</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>684</v>
+        <v>663</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>685</v>
+        <v>664</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>53</v>
@@ -8942,18 +8764,18 @@
         <v>60</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>686</v>
+        <v>665</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>672</v>
+        <v>651</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>687</v>
+        <v>666</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>688</v>
+        <v>667</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>53</v>
@@ -8962,18 +8784,18 @@
         <v>87</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>689</v>
+        <v>668</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>690</v>
+        <v>669</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>691</v>
+        <v>670</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>692</v>
+        <v>671</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>49</v>
@@ -8982,18 +8804,18 @@
         <v>60</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>693</v>
+        <v>672</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>694</v>
+        <v>673</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>695</v>
+        <v>674</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>696</v>
+        <v>675</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>49</v>
@@ -9002,18 +8824,18 @@
         <v>49</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>697</v>
+        <v>676</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>676</v>
+        <v>655</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>698</v>
+        <v>677</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>699</v>
+        <v>678</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>53</v>
@@ -9022,10 +8844,10 @@
         <v>60</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>700</v>
+        <v>679</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>701</v>
+        <v>680</v>
       </c>
     </row>
   </sheetData>
